--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128307129</v>
+        <v>135504812</v>
       </c>
       <c r="B2" t="n">
-        <v>92369</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gåltjärn, Ång</t>
+          <t>Kojtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628989</v>
+        <v>629058</v>
       </c>
       <c r="R2" t="n">
-        <v>6967511</v>
+        <v>6967527</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +770,4639 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135504817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>629105</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6967535</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135504819</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629176</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967660</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135504822</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>629212</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967707</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135504823</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629197</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135504825</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629173</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967789</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135504022</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>629084</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967545</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135504010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>629161</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967722</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135504027</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628995</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967438</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135504029</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629179</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6967610</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135504004</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>629170</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6967768</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135504030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629197</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967650</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135504031</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>629198</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967653</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128307129</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gåltjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628989</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6967511</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Amanda Selinder</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Amanda Selinder</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135504006</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>629153</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6967732</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135504014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>629145</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6967621</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135504007</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>629159</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6967723</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135504017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>629127</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6967563</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135504028</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>629059</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6967425</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135504815</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>629104</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6967454</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135504820</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>629211</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6967707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135504821</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>629216</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6967701</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135504016</v>
+      </c>
+      <c r="B24" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>629152</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6967587</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135504013</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>629140</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6967656</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135504018</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>629111</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6967556</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135504020</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>629096</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6967541</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135504021</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>629088</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6967542</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135504005</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>629139</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6967740</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135504011</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>629163</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6967691</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135504024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>629068</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6967479</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135504025</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>629058</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6967444</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sannolikt två föräldrar och en unge.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135504026</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>629013</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6967470</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135504034</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>629181</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6967762</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135504813</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>629033</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6967455</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135513904</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>629081</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6967512</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135504033</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>629192</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6967671</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>30 ex</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135504809</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>629168</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6967772</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>47 stycken blommar, ca 350 stycken totalt</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135504810</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>629133</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6967608</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>78 blommande. Dom under den fallna granen är inräknade. Ca 400 stycken totalt.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135504818</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>629141</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6967586</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>22 blommande. Ca 80 stycken.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135504824</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>629203</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6967743</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>50 stycken. 7 blommar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135504816</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>629106</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6967530</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135504811</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>629057</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6967540</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135504012</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>629140</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6967658</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504812</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504817</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504822</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504823</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504825</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504027</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504029</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504004</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504030</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307129</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2281,6 +2356,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504006</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,6 +2468,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504014</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2495,6 +2580,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504007</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2602,6 +2692,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504017</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2709,6 +2804,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504028</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2816,6 +2916,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504815</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2923,6 +3028,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504820</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504821</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3137,6 +3252,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504016</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3244,6 +3364,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504013</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3351,6 +3476,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504018</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504020</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3565,6 +3700,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504021</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3685,6 +3825,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504005</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3805,6 +3950,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504011</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3924,6 +4074,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504024</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4048,6 +4203,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4168,6 +4328,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504026</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4288,6 +4453,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504034</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4408,6 +4578,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504813</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4517,6 +4692,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513904</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4629,6 +4809,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504033</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4741,6 +4926,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504809</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4858,6 +5048,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504810</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4970,6 +5165,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504818</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5082,6 +5282,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504824</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5189,6 +5394,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504816</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5296,6 +5506,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504811</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5403,8 +5618,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504012</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504812</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504817</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504819</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504822</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504823</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504825</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504022</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504010</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504027</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504029</v>
       </c>
       <c r="B11" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504004</v>
       </c>
       <c r="B12" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504030</v>
       </c>
       <c r="B13" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504031</v>
       </c>
       <c r="B14" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135504006</v>
       </c>
       <c r="B16" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135504014</v>
       </c>
       <c r="B17" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135504007</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135504017</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135504028</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135504815</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135504820</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135504821</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135504016</v>
       </c>
       <c r="B24" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135504013</v>
       </c>
       <c r="B25" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135504018</v>
       </c>
       <c r="B26" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135504020</v>
       </c>
       <c r="B27" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135504021</v>
       </c>
       <c r="B28" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135504005</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>135504011</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135504024</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135504025</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>135504026</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135504034</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>135504813</v>
       </c>
       <c r="B35" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135513904</v>
       </c>
       <c r="B36" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135504033</v>
       </c>
       <c r="B37" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>135504809</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135504810</v>
       </c>
       <c r="B39" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135504818</v>
       </c>
       <c r="B40" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135504824</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135504816</v>
       </c>
       <c r="B42" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135504811</v>
       </c>
       <c r="B43" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>135504012</v>
       </c>
       <c r="B44" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504812</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504817</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504819</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504822</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504823</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504825</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504022</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504010</v>
       </c>
       <c r="B9" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504027</v>
       </c>
       <c r="B10" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504029</v>
       </c>
       <c r="B11" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504004</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504030</v>
       </c>
       <c r="B13" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504031</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135504006</v>
       </c>
       <c r="B16" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135504014</v>
       </c>
       <c r="B17" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135504007</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135504017</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135504028</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135504815</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135504820</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135504821</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135504016</v>
       </c>
       <c r="B24" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135504013</v>
       </c>
       <c r="B25" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135504018</v>
       </c>
       <c r="B26" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135504020</v>
       </c>
       <c r="B27" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135504021</v>
       </c>
       <c r="B28" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135504033</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>135504809</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135504810</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135504818</v>
       </c>
       <c r="B40" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135504824</v>
       </c>
       <c r="B41" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135504816</v>
       </c>
       <c r="B42" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135504811</v>
       </c>
       <c r="B43" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>135504012</v>
       </c>
       <c r="B44" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128307129</v>
+        <v>135504812</v>
       </c>
       <c r="B2" t="n">
-        <v>92369</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gåltjärn, Ång</t>
+          <t>Kojtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628989</v>
+        <v>629058</v>
       </c>
       <c r="R2" t="n">
-        <v>6967511</v>
+        <v>6967527</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,24 +775,4900 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135504812</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135504817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>629105</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6967535</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504817</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135504819</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629176</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967660</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504819</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135504822</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>629212</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967707</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504822</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135504823</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629197</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504823</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135504825</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629173</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967789</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504825</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135504022</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>629084</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967545</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135504010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>629161</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967722</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135504027</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628995</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967438</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504027</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135504029</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629179</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6967610</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504029</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135504004</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92062</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>629170</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6967768</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504004</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135504030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92062</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629197</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967650</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504030</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135504031</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92062</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>629198</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967653</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504031</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128307129</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gåltjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628989</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6967511</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128307129</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135504006</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>629153</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6967732</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504006</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135504014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>629145</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6967621</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504014</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135504007</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>629159</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6967723</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135504017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>629127</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6967563</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135504028</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>629059</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6967425</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504028</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135504815</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>629104</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6967454</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504815</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135504820</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>629211</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6967707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504820</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135504821</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>629216</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6967701</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504821</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135504016</v>
+      </c>
+      <c r="B24" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>629152</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6967587</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504016</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135504013</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80450</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>629140</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6967656</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504013</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135504018</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>629111</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6967556</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504018</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135504020</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>629096</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6967541</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504020</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135504021</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>629088</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6967542</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504021</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135504005</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>629139</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6967740</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504005</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135504011</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>629163</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6967691</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504011</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135504024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>629068</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6967479</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135504025</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>629058</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6967444</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sannolikt två föräldrar och en unge.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135504026</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>629013</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6967470</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135504034</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>629181</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6967762</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Årsfärska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504034</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135504813</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>629033</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6967455</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504813</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135513904</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Lomtjärnsåsen, Sela, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>629081</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6967512</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513904</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135504033</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>629192</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6967671</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>30 ex</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504033</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135504809</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>629168</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6967772</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>47 stycken blommar, ca 350 stycken totalt</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504809</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135504810</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>629133</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6967608</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>78 blommande. Dom under den fallna granen är inräknade. Ca 400 stycken totalt.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504810</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135504818</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>629141</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6967586</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>22 blommande. Ca 80 stycken.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504818</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135504824</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>629203</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6967743</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>50 stycken. 7 blommar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504824</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135504816</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>629106</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6967530</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504816</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135504811</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>629057</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6967540</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504811</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135504012</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kojtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>629140</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6967658</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504012</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>135504022</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504010</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504027</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504029</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504004</v>
       </c>
       <c r="B12" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504030</v>
       </c>
       <c r="B13" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504031</v>
       </c>
       <c r="B14" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135504014</v>
       </c>
       <c r="B17" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135504033</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>135504809</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135504810</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135504818</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135504824</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135504816</v>
       </c>
       <c r="B42" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135504811</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504812</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504817</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504819</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504822</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504823</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504825</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504022</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504010</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504027</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504029</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504004</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504030</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504031</v>
       </c>
       <c r="B14" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135504006</v>
       </c>
       <c r="B16" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135504014</v>
       </c>
       <c r="B17" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135504007</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135504017</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135504028</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135504815</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135504820</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135504821</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135504016</v>
       </c>
       <c r="B24" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135504013</v>
       </c>
       <c r="B25" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135504018</v>
       </c>
       <c r="B26" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135504020</v>
       </c>
       <c r="B27" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135504021</v>
       </c>
       <c r="B28" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135504005</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>135504011</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135504024</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135504025</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>135504026</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135504034</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>135504813</v>
       </c>
       <c r="B35" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135513904</v>
       </c>
       <c r="B36" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135504033</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>135504809</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135504810</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135504818</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135504824</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135504816</v>
       </c>
       <c r="B42" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135504811</v>
       </c>
       <c r="B43" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>135504012</v>
       </c>
       <c r="B44" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/S 3210-2025 artfynd.xlsx
+++ b/artfynd/S 3210-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135504812</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135504817</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135504819</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135504822</v>
       </c>
       <c r="B5" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135504823</v>
       </c>
       <c r="B6" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135504825</v>
       </c>
       <c r="B7" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135504022</v>
       </c>
       <c r="B8" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135504010</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135504027</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135504029</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135504004</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135504030</v>
       </c>
       <c r="B13" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135504031</v>
       </c>
       <c r="B14" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135504006</v>
       </c>
       <c r="B16" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135504014</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135504007</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135504017</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135504028</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135504815</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135504820</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135504821</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135504016</v>
       </c>
       <c r="B24" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135504013</v>
       </c>
       <c r="B25" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135504018</v>
       </c>
       <c r="B26" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135504020</v>
       </c>
       <c r="B27" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135504021</v>
       </c>
       <c r="B28" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135504033</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>135504809</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135504810</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135504818</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135504824</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135504816</v>
       </c>
       <c r="B42" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135504811</v>
       </c>
       <c r="B43" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>135504012</v>
       </c>
       <c r="B44" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
